--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45936.45833333334</v>
+        <v>45936.375</v>
       </c>
     </row>
     <row r="3">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45936.47916666666</v>
+        <v>45936.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45936.5625</v>
+        <v>45936.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45936.58333333334</v>
+        <v>45936.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45936.60416666666</v>
+        <v>45936.5625</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,16 +1353,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45936.625</v>
+        <v>45936.58333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45936.625</v>
+        <v>45936.60416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>3.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45936.70833333334</v>
+        <v>45936.66666666666</v>
       </c>
     </row>
     <row r="11">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45936.375</v>
+        <v>45936.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45936.45833333334</v>
+        <v>45936.47916666666</v>
       </c>
     </row>
     <row r="4">
@@ -886,7 +886,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>2.03</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45936.45833333334</v>
+        <v>45936.5625</v>
       </c>
     </row>
     <row r="5">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>3.29</v>
       </c>
       <c r="M5" t="n">
-        <v>3.87</v>
+        <v>3.68</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>1.84</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,16 +1095,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45936.47916666666</v>
+        <v>45936.58333333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.9</v>
+        <v>2.17</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="N6" t="n">
-        <v>2.03</v>
+        <v>2.92</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45936.5625</v>
+        <v>45936.60416666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1359,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45936.58333333334</v>
+        <v>45936.625</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.17</v>
+        <v>2.68</v>
       </c>
       <c r="M8" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.92</v>
+        <v>2.67</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45936.60416666666</v>
+        <v>45936.64583333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="M9" t="n">
-        <v>3.11</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>2.67</v>
+        <v>2.04</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45936.64583333334</v>
+        <v>45936.66666666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45936.66666666666</v>
+        <v>45936.70833333334</v>
       </c>
     </row>
     <row r="11">

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA5" t="n">
         <v>2.17</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -669,77 +669,77 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.85</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="N3" t="n">
         <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -936,34 +936,34 @@
         <v>2.03</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Y4" t="n">
         <v>2.4</v>
@@ -972,16 +972,16 @@
         <v>1.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1194,34 +1194,34 @@
         <v>2.92</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y6" t="n">
         <v>1.91</v>
@@ -1230,16 +1230,16 @@
         <v>1.79</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -1065,34 +1065,34 @@
         <v>1.84</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
         <v>1.45</v>
@@ -1107,10 +1107,10 @@
         <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45936.45833333334</v>
+        <v>45936.375</v>
       </c>
     </row>
     <row r="3">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45936.47916666666</v>
+        <v>45936.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -886,7 +886,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.9</v>
+        <v>1.85</v>
       </c>
       <c r="M4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.03</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>4.7</v>
+        <v>2.59</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.63</v>
+        <v>5.05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="T4" t="n">
-        <v>3.32</v>
+        <v>3.64</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.31</v>
+        <v>4.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45936.5625</v>
+        <v>45936.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.29</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>3.68</v>
+        <v>3.87</v>
       </c>
       <c r="N5" t="n">
-        <v>1.84</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.75</v>
+        <v>2.04</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>6.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.17</v>
+        <v>3.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45936.58333333334</v>
+        <v>45936.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.17</v>
+        <v>3.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>2.92</v>
+        <v>2.03</v>
       </c>
       <c r="O6" t="n">
-        <v>2.91</v>
+        <v>4.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>3.32</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="X6" t="n">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.41</v>
+        <v>4.31</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45936.60416666666</v>
+        <v>45936.5625</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45936.625</v>
+        <v>45936.58333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.68</v>
+        <v>2.17</v>
       </c>
       <c r="M8" t="n">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
       <c r="N8" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45936.64583333334</v>
+        <v>45936.60416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>3.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.04</v>
+        <v>2.67</v>
       </c>
       <c r="O9" t="n">
-        <v>3.86</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.72</v>
+        <v>3.38</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X9" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45936.66666666666</v>
+        <v>45936.64583333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45936.70833333334</v>
+        <v>45936.66666666666</v>
       </c>
     </row>
     <row r="11">

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45936.375</v>
+        <v>45936.41666666666</v>
       </c>
     </row>
     <row r="3">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.59</v>
+        <v>1.95</v>
       </c>
       <c r="P4" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.05</v>
+        <v>6.35</v>
       </c>
       <c r="R4" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>3.64</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="X4" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45936.45833333334</v>
+        <v>45936.47916666666</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,77 +1056,77 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>3.92</v>
       </c>
       <c r="M5" t="n">
-        <v>3.87</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>2.04</v>
+        <v>4.67</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.4</v>
+        <v>2.61</v>
       </c>
       <c r="R5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.36</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.29</v>
-      </c>
       <c r="X5" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH5" t="n">
-        <v>2.36</v>
+        <v>1.24</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45936.47916666666</v>
+        <v>45936.5625</v>
       </c>
     </row>
     <row r="6">
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.9</v>
+        <v>3.29</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>3.68</v>
       </c>
       <c r="N6" t="n">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>2.47</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>3.32</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="V6" t="n">
         <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>2.66</v>
+        <v>5.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.5</v>
+        <v>2.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.31</v>
+        <v>2.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45936.5625</v>
+        <v>45936.58333333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.75</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>3.66</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.25</v>
+        <v>3.64</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>5.06</v>
+        <v>3.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.21</v>
+        <v>3.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45936.58333333334</v>
+        <v>45936.60416666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
         <v>1.36</v>
@@ -1467,7 +1467,7 @@
         <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="U8" t="n">
         <v>1.4</v>
@@ -1476,28 +1476,28 @@
         <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X8" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45936.60416666666</v>
+        <v>45936.64583333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,77 +1572,77 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>2.67</v>
+        <v>2.15</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>3.74</v>
       </c>
       <c r="P9" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.38</v>
+        <v>2.72</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="T9" t="n">
         <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="AB9" t="n">
         <v>1.28</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45936.64583333334</v>
+        <v>45936.66666666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45936.66666666666</v>
+        <v>45936.79166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,126 +1789,255 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Treasure Beach</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="3" t="n">
+        <v>45936.89583333334</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Kansas City</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>5</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>3.7</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N12" t="n">
         <v>1.65</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="O12" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y12" t="n">
         <v>2</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="Z12" t="n">
         <v>1.72</v>
       </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="3" t="n">
+      <c r="AA12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3" t="n">
         <v>45936.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -1971,13 +1971,13 @@
         <v>5.42</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="Q12" t="n">
         <v>2.22</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
         <v>2.72</v>
@@ -1998,10 +1998,10 @@
         <v>3.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AA12" t="n">
         <v>3.2</v>

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
         <v>2.61</v>
@@ -816,7 +816,7 @@
         <v>5.05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S3" t="n">
         <v>2.42</v>
@@ -831,16 +831,16 @@
         <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
         <v>4.83</v>
@@ -852,7 +852,7 @@
         <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.95</v>
+        <v>3.87</v>
       </c>
       <c r="N4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
         <v>1.95</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
         <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
         <v>1.29</v>
       </c>
       <c r="X4" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z4" t="n">
         <v>1.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC4" t="n">
         <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1056,34 +1056,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q5" t="n">
         <v>2.61</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
         <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="U5" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="n">
         <v>1.03</v>
@@ -1095,22 +1095,22 @@
         <v>2.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
         <v>1.24</v>
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.29</v>
+        <v>3.85</v>
       </c>
       <c r="M6" t="n">
-        <v>3.68</v>
+        <v>3.73</v>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="R6" t="n">
         <v>1.22</v>
@@ -1209,34 +1209,34 @@
         <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
         <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>5.12</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AD6" t="n">
         <v>2.5</v>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,49 +1314,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="N7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S7" t="n">
         <v>2.9</v>
       </c>
-      <c r="O7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T7" t="n">
-        <v>2.65</v>
+        <v>2.93</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AA7" t="n">
         <v>3.3</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1443,25 +1443,25 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="O8" t="n">
         <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
         <v>2.9</v>
@@ -1482,22 +1482,22 @@
         <v>3.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AA8" t="n">
         <v>3.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
         <v>1.44</v>
@@ -1971,22 +1971,22 @@
         <v>5.42</v>
       </c>
       <c r="P12" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
         <v>2.22</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="V12" t="n">
         <v>1.03</v>
@@ -1998,7 +1998,7 @@
         <v>3.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="Z12" t="n">
         <v>1.79</v>
@@ -2013,7 +2013,7 @@
         <v>1.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>2.01</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>

--- a/jogos_2025-10-06.xlsx
+++ b/jogos_2025-10-06.xlsx
@@ -1572,19 +1572,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="O9" t="n">
         <v>3.74</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q9" t="n">
         <v>2.72</v>
@@ -1593,13 +1593,13 @@
         <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
         <v>2.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
@@ -1608,22 +1608,22 @@
         <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AA9" t="n">
         <v>3.28</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
         <v>2</v>
@@ -1642,7 +1642,7 @@
         <v>1.67</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
